--- a/output/pdf_financials_xlsx/METG.xlsx
+++ b/output/pdf_financials_xlsx/METG.xlsx
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.003477</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.053984</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.039953</v>
       </c>
     </row>
     <row r="35">
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.003477</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.053984</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.039953</v>
       </c>
     </row>
     <row r="37">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.0174</v>
+        <v>0.013923</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.110443</v>
+        <v>0.056459</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.068122</v>
+        <v>0.028169</v>
       </c>
     </row>
     <row r="49">
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.10744</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.127494</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.10744</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0.235</v>
+        <v>0.107506</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0.505421</v>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5383,7 +5383,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>-0.10744</v>
       </c>

--- a/output/pdf_financials_xlsx/METG.xlsx
+++ b/output/pdf_financials_xlsx/METG.xlsx
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0.011466</v>
+        <v>0.024297</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.02953</v>
+        <v>-0.09608</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.001522</v>
+        <v>0.109781</v>
       </c>
     </row>
     <row r="102">
@@ -4670,7 +4670,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.012831</v>
       </c>
